--- a/verification/report-samples/vehicles-full-field.xlsx
+++ b/verification/report-samples/vehicles-full-field.xlsx
@@ -7,7 +7,7 @@
     <sheet sheetId="1" name="Full-field register" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Full-field register'!$A1:$O5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Full-field register'!$A1:$V7</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Full-field register'!$1:$4</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>Gujjar Brother Transport — TEST DATA ONLY</t>
   </si>
@@ -23,49 +23,70 @@
     <t>Selected period 2026-01-01 to 2026-12-31; current master records; loans cumulative through cutoff including opening principal.</t>
   </si>
   <si>
-    <t>vehical no</t>
-  </si>
-  <si>
-    <t>company</t>
-  </si>
-  <si>
-    <t>purchase year</t>
-  </si>
-  <si>
-    <t>purchase price</t>
-  </si>
-  <si>
-    <t>income</t>
-  </si>
-  <si>
-    <t>tool</t>
-  </si>
-  <si>
-    <t>punjab police</t>
-  </si>
-  <si>
-    <t>start km</t>
-  </si>
-  <si>
-    <t>end km</t>
-  </si>
-  <si>
-    <t>total km</t>
-  </si>
-  <si>
-    <t>liter</t>
-  </si>
-  <si>
-    <t>km</t>
-  </si>
-  <si>
-    <t>ave</t>
-  </si>
-  <si>
-    <t>major maintenence work</t>
-  </si>
-  <si>
-    <t>remarks</t>
+    <t>Vehicle number</t>
+  </si>
+  <si>
+    <t>Company / manufacturer</t>
+  </si>
+  <si>
+    <t>Model</t>
+  </si>
+  <si>
+    <t>Vehicle status</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>Opening odometer (km)</t>
+  </si>
+  <si>
+    <t>Service interval (km)</t>
+  </si>
+  <si>
+    <t>Document expiry</t>
+  </si>
+  <si>
+    <t>Permit expiry</t>
+  </si>
+  <si>
+    <t>Insurance expiry</t>
+  </si>
+  <si>
+    <t>Purchase year</t>
+  </si>
+  <si>
+    <t>Purchase price (PKR)</t>
+  </si>
+  <si>
+    <t>Revenue (PKR)</t>
+  </si>
+  <si>
+    <t>Tolls (PKR)</t>
+  </si>
+  <si>
+    <t>Punjab Police (PKR)</t>
+  </si>
+  <si>
+    <t>Start odometer (km)</t>
+  </si>
+  <si>
+    <t>End odometer (km)</t>
+  </si>
+  <si>
+    <t>Total distance (km)</t>
+  </si>
+  <si>
+    <t>Matched fuel (litres)</t>
+  </si>
+  <si>
+    <t>Average (km/L)</t>
+  </si>
+  <si>
+    <t>Major maintenance work</t>
+  </si>
+  <si>
+    <t>Remarks</t>
   </si>
   <si>
     <t>TEST-001</t>
@@ -74,19 +95,26 @@
     <t>TEST Manufacturer</t>
   </si>
   <si>
+    <t>Active</t>
+  </si>
+  <si>
     <t>TEST overhaul notes</t>
   </si>
   <si>
     <t>TEST vehicle remarks</t>
+  </si>
+  <si>
+    <t>Signature: __________________________</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00;[Red]-#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="0.###"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.###"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00;[Red]-#,##0.00"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -129,25 +157,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -156,13 +188,16 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -171,13 +206,16 @@
     <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="1" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -201,7 +239,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>14</xdr:col>
+      <xdr:col>21</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -566,151 +604,228 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:V7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="2" width="22" style="1" customWidth="1"/>
-    <col min="3" max="3" width="22" style="2" customWidth="1"/>
-    <col min="4" max="7" width="22" style="3" customWidth="1"/>
-    <col min="8" max="13" width="22" style="4" customWidth="1"/>
-    <col min="14" max="14" width="30" style="1" customWidth="1"/>
-    <col min="15" max="15" width="22" style="1" customWidth="1"/>
+    <col min="1" max="1" width="22" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30" style="1" customWidth="1"/>
+    <col min="3" max="5" width="22" style="1" customWidth="1"/>
+    <col min="6" max="7" width="30" style="2" customWidth="1"/>
+    <col min="8" max="10" width="22" style="3" customWidth="1"/>
+    <col min="11" max="11" width="22" style="4" customWidth="1"/>
+    <col min="12" max="12" width="30" style="5" customWidth="1"/>
+    <col min="13" max="14" width="22" style="5" customWidth="1"/>
+    <col min="15" max="15" width="30" style="5" customWidth="1"/>
+    <col min="16" max="19" width="30" style="2" customWidth="1"/>
+    <col min="20" max="20" width="22" style="2" customWidth="1"/>
+    <col min="21" max="21" width="30" style="1" customWidth="1"/>
+    <col min="22" max="22" width="22" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:22" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6"/>
+      <c r="B1" s="7"/>
       <c r="C1" s="7"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
       <c r="H1" s="9"/>
       <c r="I1" s="9"/>
       <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="8"/>
+      <c r="R1" s="8"/>
+      <c r="S1" s="8"/>
+      <c r="T1" s="8"/>
+      <c r="U1" s="7"/>
+      <c r="V1" s="7"/>
     </row>
-    <row r="2" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
+    <row r="2" spans="1:22" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="12"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
       <c r="D2" s="13"/>
       <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14"/>
-      <c r="M2" s="14"/>
-      <c r="N2" s="11"/>
-      <c r="O2" s="11"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="14"/>
+      <c r="R2" s="14"/>
+      <c r="S2" s="14"/>
+      <c r="T2" s="14"/>
+      <c r="U2" s="13"/>
+      <c r="V2" s="13"/>
     </row>
-    <row r="4" ht="40" customHeight="1" spans="1:15" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
+    <row r="4" ht="40" customHeight="1" spans="1:22" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="18" t="s">
+      <c r="G4" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="19" t="s">
+      <c r="H4" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="19" t="s">
+      <c r="I4" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="19" t="s">
+      <c r="J4" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="19" t="s">
+      <c r="K4" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="L4" s="19" t="s">
+      <c r="L4" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="M4" s="19" t="s">
+      <c r="M4" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="N4" s="16" t="s">
+      <c r="N4" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="O4" s="16" t="s">
+      <c r="O4" s="23" t="s">
         <v>16</v>
       </c>
+      <c r="P4" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q4" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="R4" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="S4" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="T4" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="U4" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="V4" s="19" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="5" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="12">
+    <row r="5" spans="1:22" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="13"/>
+      <c r="F5" s="14">
+        <v>0</v>
+      </c>
+      <c r="G5" s="14"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="16">
         <v>2020</v>
       </c>
-      <c r="D5" s="13">
+      <c r="L5" s="17">
         <v>1234567.89</v>
       </c>
-      <c r="E5" s="13">
+      <c r="M5" s="17">
         <v>80000</v>
       </c>
-      <c r="F5" s="13">
+      <c r="N5" s="17">
         <v>3000</v>
       </c>
-      <c r="G5" s="13">
+      <c r="O5" s="17">
         <v>0</v>
       </c>
-      <c r="H5" s="14">
+      <c r="P5" s="14">
         <v>144844</v>
       </c>
-      <c r="I5" s="14">
+      <c r="Q5" s="14">
         <v>145382</v>
       </c>
-      <c r="J5" s="14">
+      <c r="R5" s="14">
         <v>538</v>
       </c>
-      <c r="K5" s="14">
+      <c r="S5" s="14">
         <v>68</v>
       </c>
-      <c r="L5" s="14">
-        <v>538</v>
-      </c>
-      <c r="M5" s="14">
+      <c r="T5" s="14">
         <v>7.91</v>
       </c>
-      <c r="N5" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="O5" s="11" t="s">
-        <v>20</v>
-      </c>
+      <c r="U5" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="V5" s="13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="15"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="16"/>
+      <c r="L7" s="17"/>
+      <c r="M7" s="17"/>
+      <c r="N7" s="17"/>
+      <c r="O7" s="17"/>
+      <c r="P7" s="14"/>
+      <c r="Q7" s="14"/>
+      <c r="R7" s="14"/>
+      <c r="S7" s="14"/>
+      <c r="T7" s="14"/>
+      <c r="U7" s="13"/>
+      <c r="V7" s="13"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:O4"/>
+  <autoFilter ref="A4:V4"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <drawing r:id="rId1"/>
 </worksheet>
